--- a/artfynd/A 25488-2026 artfynd.xlsx
+++ b/artfynd/A 25488-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665677</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665678</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665679</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665680</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1226,6 +1251,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665676</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1346,8 +1376,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665675</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 25488-2026 artfynd.xlsx
+++ b/artfynd/A 25488-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134665677</v>
       </c>
       <c r="B2" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134665678</v>
       </c>
       <c r="B3" t="n">
-        <v>92392</v>
+        <v>92394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25488-2026 artfynd.xlsx
+++ b/artfynd/A 25488-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134665677</v>
       </c>
       <c r="B2" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134665678</v>
       </c>
       <c r="B3" t="n">
-        <v>92394</v>
+        <v>92406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>134665679</v>
       </c>
       <c r="B4" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>134665680</v>
       </c>
       <c r="B5" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>134665676</v>
       </c>
       <c r="B6" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>134665675</v>
       </c>
       <c r="B7" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 25488-2026 artfynd.xlsx
+++ b/artfynd/A 25488-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134665677</v>
       </c>
       <c r="B2" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134665678</v>
       </c>
       <c r="B3" t="n">
-        <v>92406</v>
+        <v>92407</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>134665679</v>
       </c>
       <c r="B4" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>134665680</v>
       </c>
       <c r="B5" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25488-2026 artfynd.xlsx
+++ b/artfynd/A 25488-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134665677</v>
       </c>
       <c r="B2" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134665678</v>
       </c>
       <c r="B3" t="n">
-        <v>92407</v>
+        <v>92408</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
